--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261005.xlsx
@@ -7580,7 +7580,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>計画素案（第7版）</t>
+          <t>計画素案（第10版）</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -7590,11 +7590,11 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第9版_20261005.docx</t>
+          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第10版_20261014.docx</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5</v>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>26</v>

--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261005.xlsx
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6000</v>
+        <v>5200</v>
       </c>
       <c r="C7" s="6" t="n"/>
     </row>
@@ -7580,7 +7580,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>計画素案（第10版）</t>
+          <t>計画素案（第15版）</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -7590,11 +7590,11 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第10版_20261014.docx</t>
+          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第15版_20261021.docx</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5</v>
@@ -7838,7 +7838,7 @@
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="n">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>26</v>

--- a/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261005.xlsx
+++ b/小野町_引継ぎ_整理済/22_図表管理/小野町_第10期計画_図表データ管理台帳_20261005.xlsx
@@ -7580,7 +7580,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>計画素案（第15版）</t>
+          <t>計画素案（第16版）</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -7590,11 +7590,11 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第15版_20261021.docx</t>
+          <t>小野町高齢者保健福祉計画_第10期介護保険事業計画_素案_第16版_20261022.docx</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5</v>
@@ -7838,7 +7838,7 @@
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>26</v>
